--- a/Mappe.xlsx
+++ b/Mappe.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Edoardo\.gemini\antigravity\scratch\DASHBOARD_MAPPE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3446DF2D-633C-4E78-BD61-954B7FE8DE96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72D84A52-10CA-43FE-B174-C04325B186C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Note" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Brasile!$A$2:$M$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Brasile!$A$2:$N$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
   <si>
     <t>ANNO</t>
   </si>
@@ -712,6 +712,9 @@
   </si>
   <si>
     <t>E' sufficiente inserire nel foglio Excel il nome della città, affinché il sistema compili in automatico, lo Stato, La Regione e la Provincia.</t>
+  </si>
+  <si>
+    <t>CORTESIA</t>
   </si>
 </sst>
 </file>
@@ -816,7 +819,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -841,6 +844,15 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1156,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:M33"/>
+  <dimension ref="A2:N33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="2" customWidth="1"/>
@@ -1167,11 +1179,13 @@
     <col min="7" max="7" width="15.7109375" customWidth="1"/>
     <col min="8" max="8" width="16.7109375" customWidth="1"/>
     <col min="9" max="9" width="16.7109375" style="6" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" style="6" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="9.140625" style="2"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1211,8 +1225,11 @@
       <c r="M2" s="4" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N2" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2026</v>
       </c>
@@ -1250,12 +1267,12 @@
       <c r="L3" s="6">
         <v>100</v>
       </c>
-      <c r="M3" s="3">
+      <c r="M3" s="13">
         <f t="shared" ref="M3:M21" si="1">L3/$I$33</f>
         <v>2.8169014084507043E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2026</v>
       </c>
@@ -1293,12 +1310,12 @@
       <c r="L4" s="6">
         <v>200</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>2026</v>
       </c>
@@ -1336,12 +1353,12 @@
       <c r="L5" s="6">
         <v>300</v>
       </c>
-      <c r="M5" s="3">
+      <c r="M5" s="13">
         <f t="shared" si="1"/>
         <v>8.4507042253521125E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>2026</v>
       </c>
@@ -1379,12 +1396,12 @@
       <c r="L6" s="6">
         <v>200</v>
       </c>
-      <c r="M6" s="3">
+      <c r="M6" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>2026</v>
       </c>
@@ -1422,12 +1439,12 @@
       <c r="L7" s="6">
         <v>100</v>
       </c>
-      <c r="M7" s="3">
+      <c r="M7" s="13">
         <f t="shared" si="1"/>
         <v>2.8169014084507043E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>2026</v>
       </c>
@@ -1465,12 +1482,12 @@
       <c r="L8" s="6">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>2026</v>
       </c>
@@ -1508,12 +1525,12 @@
       <c r="L9" s="6">
         <v>300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="13">
         <f t="shared" si="1"/>
         <v>8.4507042253521125E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>2026</v>
       </c>
@@ -1551,12 +1568,12 @@
       <c r="L10" s="6">
         <v>200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>2026</v>
       </c>
@@ -1594,12 +1611,12 @@
       <c r="L11" s="6">
         <v>100</v>
       </c>
-      <c r="M11" s="3">
+      <c r="M11" s="13">
         <f t="shared" si="1"/>
         <v>2.8169014084507043E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>2026</v>
       </c>
@@ -1637,12 +1654,12 @@
       <c r="L12" s="6">
         <v>50</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="13">
         <f t="shared" si="1"/>
         <v>1.4084507042253521E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>2026</v>
       </c>
@@ -1680,12 +1697,12 @@
       <c r="L13" s="6">
         <v>200</v>
       </c>
-      <c r="M13" s="3">
+      <c r="M13" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>2026</v>
       </c>
@@ -1723,12 +1740,12 @@
       <c r="L14" s="6">
         <v>200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>2026</v>
       </c>
@@ -1761,17 +1778,20 @@
         <v>5.6338028169014086E-2</v>
       </c>
       <c r="K15" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="L15" s="6">
         <v>200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="M15" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>2026</v>
       </c>
@@ -1809,7 +1829,7 @@
       <c r="L16" s="6">
         <v>200</v>
       </c>
-      <c r="M16" s="3">
+      <c r="M16" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
@@ -1852,7 +1872,7 @@
       <c r="L17" s="6">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
@@ -1895,7 +1915,7 @@
       <c r="L18" s="6">
         <v>200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
@@ -1938,7 +1958,7 @@
       <c r="L19" s="6">
         <v>200</v>
       </c>
-      <c r="M19" s="3">
+      <c r="M19" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
@@ -1981,7 +2001,7 @@
       <c r="L20" s="6">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
@@ -2024,7 +2044,7 @@
       <c r="L21" s="6">
         <v>200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="13">
         <f t="shared" si="1"/>
         <v>5.6338028169014086E-2</v>
       </c>
@@ -2033,7 +2053,7 @@
       <c r="I32" s="7"/>
       <c r="J32" s="1"/>
       <c r="L32" s="7"/>
-      <c r="M32" s="1"/>
+      <c r="M32" s="14"/>
     </row>
     <row r="33" spans="9:13" x14ac:dyDescent="0.25">
       <c r="I33" s="8">
@@ -2048,13 +2068,13 @@
         <f>SUM(L3:L32)</f>
         <v>3550</v>
       </c>
-      <c r="M33" s="9">
+      <c r="M33" s="15">
         <f>SUM(M3:M32)</f>
         <v>1.0000000000000002</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:M21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:N2" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
